--- a/age_mort_background_costs.xlsx
+++ b/age_mort_background_costs.xlsx
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Table 1'!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <webPublishing codePage="1252"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -506,16 +506,16 @@
         <v>2477.51806640625</v>
       </c>
       <c r="F2" s="10">
-        <f>C2*(116/103)*(126.919/116.048)</f>
-        <v>2539.5355607108791</v>
+        <f>C2*(116/103)*(118.896/116.048)</f>
+        <v>2379.002513621134</v>
       </c>
       <c r="G2" s="10">
-        <f>D2*(116/103)*(126.919/116.048)</f>
-        <v>1913.2155735295582</v>
+        <f>D2*(116/103)*(118.896/116.048)</f>
+        <v>1792.2744335392683</v>
       </c>
       <c r="H2" s="10">
-        <f>E2*(116/103)*(126.919/116.048)</f>
-        <v>3051.5927619626523</v>
+        <f>E2*(116/103)*(118.896/116.048)</f>
+        <v>2858.690763607589</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
@@ -535,16 +535,16 @@
         <v>2418.05004882812</v>
       </c>
       <c r="F3" s="10">
-        <f t="shared" ref="F3:F66" si="0">C3*(116/103)*(126.919/116.048)</f>
-        <v>2518.8659406274683</v>
+        <f t="shared" ref="F3:F66" si="0">C3*(116/103)*(118.896/116.048)</f>
+        <v>2359.6394935103767</v>
       </c>
       <c r="G3" s="10">
-        <f t="shared" ref="G3:G66" si="1">D3*(116/103)*(126.919/116.048)</f>
-        <v>1974.5981243414014</v>
+        <f t="shared" ref="G3:G66" si="1">D3*(116/103)*(118.896/116.048)</f>
+        <v>1849.7767756734238</v>
       </c>
       <c r="H3" s="10">
-        <f t="shared" ref="H3:H66" si="2">E3*(116/103)*(126.919/116.048)</f>
-        <v>2978.3451943786458</v>
+        <f t="shared" ref="H3:H66" si="2">E3*(116/103)*(118.896/116.048)</f>
+        <v>2790.073434480602</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
@@ -565,15 +565,15 @@
       </c>
       <c r="F4" s="10">
         <f t="shared" si="0"/>
-        <v>2505.5803455162113</v>
+        <v>2347.1937279721355</v>
       </c>
       <c r="G4" s="10">
         <f t="shared" si="1"/>
-        <v>2039.8427108230335</v>
+        <v>1910.8970205092648</v>
       </c>
       <c r="H4" s="10">
         <f t="shared" si="2"/>
-        <v>2922.0090308277622</v>
+        <v>2737.298479575931</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -594,15 +594,15 @@
       </c>
       <c r="F5" s="10">
         <f t="shared" si="0"/>
-        <v>2499.7649838755856</v>
+        <v>2341.7459759600342</v>
       </c>
       <c r="G5" s="10">
         <f t="shared" si="1"/>
-        <v>2102.2347495849958</v>
+        <v>1969.3450372809245</v>
       </c>
       <c r="H5" s="10">
         <f t="shared" si="2"/>
-        <v>2877.1326755257032</v>
+        <v>2695.2589178082403</v>
       </c>
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
@@ -625,15 +625,15 @@
       </c>
       <c r="F6" s="10">
         <f t="shared" si="0"/>
-        <v>2499.0026828883706</v>
+        <v>2341.031862721072</v>
       </c>
       <c r="G6" s="10">
         <f t="shared" si="1"/>
-        <v>2161.7258261024549</v>
+        <v>2025.0754719173449</v>
       </c>
       <c r="H6" s="10">
         <f t="shared" si="2"/>
-        <v>2841.0482175122465</v>
+        <v>2661.4554863285725</v>
       </c>
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
@@ -656,15 +656,15 @@
       </c>
       <c r="F7" s="10">
         <f t="shared" si="0"/>
-        <v>2502.9236116485913</v>
+        <v>2344.7049356721286</v>
       </c>
       <c r="G7" s="10">
         <f t="shared" si="1"/>
-        <v>2197.8229139919631</v>
+        <v>2058.890734893818</v>
       </c>
       <c r="H7" s="10">
         <f t="shared" si="2"/>
-        <v>2816.0299366106674</v>
+        <v>2638.0186996687803</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
@@ -685,15 +685,15 @@
       </c>
       <c r="F8" s="10">
         <f t="shared" si="0"/>
-        <v>2511.108693884787</v>
+        <v>2352.3726098387606</v>
       </c>
       <c r="G8" s="10">
         <f t="shared" si="1"/>
-        <v>2233.1080812781661</v>
+        <v>2091.945401647104</v>
       </c>
       <c r="H8" s="10">
         <f t="shared" si="2"/>
-        <v>2801.1732931266142</v>
+        <v>2624.1011972957713</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
@@ -714,15 +714,15 @@
       </c>
       <c r="F9" s="10">
         <f t="shared" si="0"/>
-        <v>2524.2743737093333</v>
+        <v>2364.706040360741</v>
       </c>
       <c r="G9" s="10">
         <f t="shared" si="1"/>
-        <v>2269.1958471163093</v>
+        <v>2125.7519318521317</v>
       </c>
       <c r="H9" s="10">
         <f t="shared" si="2"/>
-        <v>2792.2331451500922</v>
+        <v>2615.7261877714554</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
@@ -743,15 +743,15 @@
       </c>
       <c r="F10" s="10">
         <f t="shared" si="0"/>
-        <v>2541.9856081308708</v>
+        <v>2381.297684856704</v>
       </c>
       <c r="G10" s="10">
         <f t="shared" si="1"/>
-        <v>2307.1496771410812</v>
+        <v>2161.3065657101456</v>
       </c>
       <c r="H10" s="10">
         <f t="shared" si="2"/>
-        <v>2788.9033685424783</v>
+        <v>2612.6068981494222</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
@@ -772,15 +772,15 @@
       </c>
       <c r="F11" s="10">
         <f t="shared" si="0"/>
-        <v>2564.4018518831799</v>
+        <v>2402.2969183613372</v>
       </c>
       <c r="G11" s="10">
         <f t="shared" si="1"/>
-        <v>2347.8181787386043</v>
+        <v>2199.4042671255297</v>
       </c>
       <c r="H11" s="10">
         <f t="shared" si="2"/>
-        <v>2791.4146088974016</v>
+        <v>2614.9593940975383</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
@@ -801,15 +801,15 @@
       </c>
       <c r="F12" s="10">
         <f t="shared" si="0"/>
-        <v>2592.1515206542022</v>
+        <v>2428.2924321788073</v>
       </c>
       <c r="G12" s="10">
         <f t="shared" si="1"/>
-        <v>2391.8835155713423</v>
+        <v>2240.684077776931</v>
       </c>
       <c r="H12" s="10">
         <f t="shared" si="2"/>
-        <v>2809.8623471387959</v>
+        <v>2632.2409853955223</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
@@ -830,15 +830,15 @@
       </c>
       <c r="F13" s="10">
         <f t="shared" si="0"/>
-        <v>2625.3991069721037</v>
+        <v>2459.438320681342</v>
       </c>
       <c r="G13" s="10">
         <f t="shared" si="1"/>
-        <v>2439.5079214043067</v>
+        <v>2285.297976057852</v>
       </c>
       <c r="H13" s="10">
         <f t="shared" si="2"/>
-        <v>2837.8642859019019</v>
+        <v>2658.4728223244156</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
@@ -859,15 +859,15 @@
       </c>
       <c r="F14" s="10">
         <f t="shared" si="0"/>
-        <v>2663.7310190185963</v>
+        <v>2495.3471366559384</v>
       </c>
       <c r="G14" s="10">
         <f t="shared" si="1"/>
-        <v>2495.7101180556529</v>
+        <v>2337.9474325857036</v>
       </c>
       <c r="H14" s="10">
         <f t="shared" si="2"/>
-        <v>2870.8093175825293</v>
+        <v>2689.3352817410505</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
@@ -888,15 +888,15 @@
       </c>
       <c r="F15" s="10">
         <f t="shared" si="0"/>
-        <v>2707.5272947159042</v>
+        <v>2536.374894480276</v>
       </c>
       <c r="G15" s="10">
         <f t="shared" si="1"/>
-        <v>2553.6235125563221</v>
+        <v>2392.199916079519</v>
       </c>
       <c r="H15" s="10">
         <f t="shared" si="2"/>
-        <v>2908.6664689132358</v>
+        <v>2724.79934830804</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
@@ -917,15 +917,15 @@
       </c>
       <c r="F16" s="10">
         <f t="shared" si="0"/>
-        <v>2756.8338171405921</v>
+        <v>2582.5645767989654</v>
       </c>
       <c r="G16" s="10">
         <f t="shared" si="1"/>
-        <v>2615.355640294591</v>
+        <v>2450.0297371431043</v>
       </c>
       <c r="H16" s="10">
         <f t="shared" si="2"/>
-        <v>2941.0305262954889</v>
+        <v>2755.1175588716305</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -946,15 +946,15 @@
       </c>
       <c r="F17" s="10">
         <f t="shared" si="0"/>
-        <v>2811.9066813469253</v>
+        <v>2634.156089989868</v>
       </c>
       <c r="G17" s="10">
         <f t="shared" si="1"/>
-        <v>2677.0002610345077</v>
+        <v>2507.777582835973</v>
       </c>
       <c r="H17" s="10">
         <f t="shared" si="2"/>
-        <v>2978.3073047505031</v>
+        <v>2790.0379399901976</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -975,15 +975,15 @@
       </c>
       <c r="F18" s="10">
         <f t="shared" si="0"/>
-        <v>2870.3036391356677</v>
+        <v>2688.861569021773</v>
       </c>
       <c r="G18" s="10">
         <f t="shared" si="1"/>
-        <v>2736.5275732677665</v>
+        <v>2563.541962600118</v>
       </c>
       <c r="H18" s="10">
         <f t="shared" si="2"/>
-        <v>3021.4461499614617</v>
+        <v>2830.449825840244</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -1004,15 +1004,15 @@
       </c>
       <c r="F19" s="10">
         <f t="shared" si="0"/>
-        <v>2933.0487995987892</v>
+        <v>2747.640385419816</v>
       </c>
       <c r="G19" s="10">
         <f t="shared" si="1"/>
-        <v>2802.3241154039902</v>
+        <v>2625.179272016584</v>
       </c>
       <c r="H19" s="10">
         <f t="shared" si="2"/>
-        <v>3068.9537294409392</v>
+        <v>2874.9542827757073</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -1033,15 +1033,15 @@
       </c>
       <c r="F20" s="10">
         <f t="shared" si="0"/>
-        <v>3000.1876199078974</v>
+        <v>2810.5351228466143</v>
       </c>
       <c r="G20" s="10">
         <f t="shared" si="1"/>
-        <v>2872.1225239805681</v>
+        <v>2690.565475706503</v>
       </c>
       <c r="H20" s="10">
         <f t="shared" si="2"/>
-        <v>3122.1558794630164</v>
+        <v>2924.793336258833</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -1062,15 +1062,15 @@
       </c>
       <c r="F21" s="10">
         <f t="shared" si="0"/>
-        <v>3071.0194865172384</v>
+        <v>2876.8894560227673</v>
       </c>
       <c r="G21" s="10">
         <f t="shared" si="1"/>
-        <v>2943.6464141948522</v>
+        <v>2757.568087221859</v>
       </c>
       <c r="H21" s="10">
         <f t="shared" si="2"/>
-        <v>3192.5587178220517</v>
+        <v>2990.7457615815656</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -1091,15 +1091,15 @@
       </c>
       <c r="F22" s="10">
         <f t="shared" si="0"/>
-        <v>3145.5145055223734</v>
+        <v>2946.6753807435307</v>
       </c>
       <c r="G22" s="10">
         <f t="shared" si="1"/>
-        <v>3015.7500758621718</v>
+        <v>2825.1138207810395</v>
       </c>
       <c r="H22" s="10">
         <f t="shared" si="2"/>
-        <v>3269.3808410399934</v>
+        <v>3062.711686006753</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -1120,15 +1120,15 @@
       </c>
       <c r="F23" s="10">
         <f t="shared" si="0"/>
-        <v>3221.4934500778677</v>
+        <v>3017.851426819138</v>
       </c>
       <c r="G23" s="10">
         <f t="shared" si="1"/>
-        <v>3098.6961854084793</v>
+        <v>2902.816612645282</v>
       </c>
       <c r="H23" s="10">
         <f t="shared" si="2"/>
-        <v>3354.4430562476214</v>
+        <v>3142.3968169904997</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -1149,15 +1149,15 @@
       </c>
       <c r="F24" s="10">
         <f t="shared" si="0"/>
-        <v>3299.9241448781895</v>
+        <v>3091.3242393135565</v>
       </c>
       <c r="G24" s="10">
         <f t="shared" si="1"/>
-        <v>3187.1110312851224</v>
+        <v>2985.64244262621</v>
       </c>
       <c r="H24" s="10">
         <f t="shared" si="2"/>
-        <v>3442.2564794551408</v>
+        <v>3224.659242361651</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -1178,15 +1178,15 @@
       </c>
       <c r="F25" s="10">
         <f t="shared" si="0"/>
-        <v>3381.7669534194752</v>
+        <v>3167.99347374122</v>
       </c>
       <c r="G25" s="10">
         <f t="shared" si="1"/>
-        <v>3265.7431360258006</v>
+        <v>3059.3039332245257</v>
       </c>
       <c r="H25" s="10">
         <f t="shared" si="2"/>
-        <v>3533.8372142620551</v>
+        <v>3310.4508342084428</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -1207,15 +1207,15 @@
       </c>
       <c r="F26" s="10">
         <f t="shared" si="0"/>
-        <v>3468.2117079457503</v>
+        <v>3248.9737488312853</v>
       </c>
       <c r="G26" s="10">
         <f t="shared" si="1"/>
-        <v>3348.8729801975196</v>
+        <v>3137.178845197049</v>
       </c>
       <c r="H26" s="10">
         <f t="shared" si="2"/>
-        <v>3624.1330095364042</v>
+        <v>3395.0387121064646</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -1236,15 +1236,15 @@
       </c>
       <c r="F27" s="10">
         <f t="shared" si="0"/>
-        <v>3559.3759451610958</v>
+        <v>3334.3751713760244</v>
       </c>
       <c r="G27" s="10">
         <f t="shared" si="1"/>
-        <v>3435.9280094192727</v>
+        <v>3218.730817355273</v>
       </c>
       <c r="H27" s="10">
         <f t="shared" si="2"/>
-        <v>3716.2908093943379</v>
+        <v>3481.370890676331</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -1265,15 +1265,15 @@
       </c>
       <c r="F28" s="10">
         <f t="shared" si="0"/>
-        <v>3656.0655147824241</v>
+        <v>3424.9526504744845</v>
       </c>
       <c r="G28" s="10">
         <f t="shared" si="1"/>
-        <v>3529.1635587003016</v>
+        <v>3306.0726169858817</v>
       </c>
       <c r="H28" s="10">
         <f t="shared" si="2"/>
-        <v>3814.8537606784712</v>
+        <v>3573.7033283403393</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -1294,15 +1294,15 @@
       </c>
       <c r="F29" s="10">
         <f t="shared" si="0"/>
-        <v>3757.1053570683257</v>
+        <v>3519.605406077858</v>
       </c>
       <c r="G29" s="10">
         <f t="shared" si="1"/>
-        <v>3626.0377151295093</v>
+        <v>3396.823014505615</v>
       </c>
       <c r="H29" s="10">
         <f t="shared" si="2"/>
-        <v>3917.1653794592453</v>
+        <v>3669.5474669370733</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -1323,15 +1323,15 @@
       </c>
       <c r="F30" s="10">
         <f t="shared" si="0"/>
-        <v>3863.0312822737733</v>
+        <v>3618.835377975107</v>
       </c>
       <c r="G30" s="10">
         <f t="shared" si="1"/>
-        <v>3727.4727603700399</v>
+        <v>3491.8459908836053</v>
       </c>
       <c r="H30" s="10">
         <f t="shared" si="2"/>
-        <v>4037.6441728062487</v>
+        <v>3782.410368581314</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -1352,15 +1352,15 @@
       </c>
       <c r="F31" s="10">
         <f t="shared" si="0"/>
-        <v>3973.0314072379424</v>
+        <v>3721.882005018653</v>
       </c>
       <c r="G31" s="10">
         <f t="shared" si="1"/>
-        <v>3834.0493680089039</v>
+        <v>3591.6855132705637</v>
       </c>
       <c r="H31" s="10">
         <f t="shared" si="2"/>
-        <v>4162.4580207523259</v>
+        <v>3899.334290652846</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -1381,15 +1381,15 @@
       </c>
       <c r="F32" s="10">
         <f t="shared" si="0"/>
-        <v>4092.6534257264352</v>
+        <v>3833.9422915810105</v>
       </c>
       <c r="G32" s="10">
         <f t="shared" si="1"/>
-        <v>3952.1805079669984</v>
+        <v>3702.3491650205588</v>
       </c>
       <c r="H32" s="10">
         <f t="shared" si="2"/>
-        <v>4295.3095819598975</v>
+        <v>4023.7878336317185</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -1410,15 +1410,15 @@
       </c>
       <c r="F33" s="10">
         <f t="shared" si="0"/>
-        <v>4224.1698235010172</v>
+        <v>3957.14507154151</v>
       </c>
       <c r="G33" s="10">
         <f t="shared" si="1"/>
-        <v>4080.111228895807</v>
+        <v>3822.1929314822514</v>
       </c>
       <c r="H33" s="10">
         <f t="shared" si="2"/>
-        <v>4439.4131598841323</v>
+        <v>4158.78211345491</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -1439,15 +1439,15 @@
       </c>
       <c r="F34" s="10">
         <f t="shared" si="0"/>
-        <v>4357.6920820114765</v>
+        <v>4082.2269146686986</v>
       </c>
       <c r="G34" s="10">
         <f t="shared" si="1"/>
-        <v>4209.3449320372674</v>
+        <v>3943.2573140310196</v>
       </c>
       <c r="H34" s="10">
         <f t="shared" si="2"/>
-        <v>4587.8063849958771</v>
+        <v>4297.794876657315</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -1468,15 +1468,15 @@
       </c>
       <c r="F35" s="10">
         <f t="shared" si="0"/>
-        <v>4498.7242989731176</v>
+        <v>4214.343985145706</v>
       </c>
       <c r="G35" s="10">
         <f t="shared" si="1"/>
-        <v>4345.0511459438449</v>
+        <v>4070.3850569902015</v>
       </c>
       <c r="H35" s="10">
         <f t="shared" si="2"/>
-        <v>4737.2923950974337</v>
+        <v>4437.831346035697</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -1497,15 +1497,15 @@
       </c>
       <c r="F36" s="10">
         <f t="shared" si="0"/>
-        <v>4653.4983845268043</v>
+        <v>4359.334251977238</v>
       </c>
       <c r="G36" s="10">
         <f t="shared" si="1"/>
-        <v>4484.7468971260532</v>
+        <v>4201.250144428331</v>
       </c>
       <c r="H36" s="10">
         <f t="shared" si="2"/>
-        <v>4889.6387714133461</v>
+        <v>4580.547367738174</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -1526,15 +1526,15 @@
       </c>
       <c r="F37" s="10">
         <f t="shared" si="0"/>
-        <v>4810.7019141576066</v>
+        <v>4506.600389111818</v>
       </c>
       <c r="G37" s="10">
         <f t="shared" si="1"/>
-        <v>4650.2869832458773</v>
+        <v>4356.325854757773</v>
       </c>
       <c r="H37" s="10">
         <f t="shared" si="2"/>
-        <v>5045.6342797741781</v>
+        <v>4726.681846910476</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -1555,15 +1555,15 @@
       </c>
       <c r="F38" s="10">
         <f t="shared" si="0"/>
-        <v>4980.128692053976</v>
+        <v>4665.317099649774</v>
       </c>
       <c r="G38" s="10">
         <f t="shared" si="1"/>
-        <v>4806.6905568877037</v>
+        <v>4502.8426039578035</v>
       </c>
       <c r="H38" s="10">
         <f t="shared" si="2"/>
-        <v>5216.3192361170331</v>
+        <v>4886.577201974258</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -1584,15 +1584,15 @@
       </c>
       <c r="F39" s="10">
         <f t="shared" si="0"/>
-        <v>5159.5289438213576</v>
+        <v>4833.376825412934</v>
       </c>
       <c r="G39" s="10">
         <f t="shared" si="1"/>
-        <v>4981.5938918317979</v>
+        <v>4666.689678954557</v>
       </c>
       <c r="H39" s="10">
         <f t="shared" si="2"/>
-        <v>5400.077918441315</v>
+        <v>5058.71984644536</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -1613,15 +1613,15 @@
       </c>
       <c r="F40" s="10">
         <f t="shared" si="0"/>
-        <v>5354.5425839027957</v>
+        <v>5016.062961855253</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="1"/>
-        <v>5162.1960072771863</v>
+        <v>4835.875294331254</v>
       </c>
       <c r="H40" s="10">
         <f t="shared" si="2"/>
-        <v>5604.6043269531347</v>
+        <v>5250.317415496655</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -1642,15 +1642,15 @@
       </c>
       <c r="F41" s="10">
         <f t="shared" si="0"/>
-        <v>5563.7786200300834</v>
+        <v>5212.072446261764</v>
       </c>
       <c r="G41" s="10">
         <f t="shared" si="1"/>
-        <v>5362.9382643548743</v>
+        <v>5023.927921577834</v>
       </c>
       <c r="H41" s="10">
         <f t="shared" si="2"/>
-        <v>5822.0962053659377</v>
+        <v>5454.060861125509</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -1671,15 +1671,15 @@
       </c>
       <c r="F42" s="10">
         <f t="shared" si="0"/>
-        <v>5784.1750943942361</v>
+        <v>5418.536878033211</v>
       </c>
       <c r="G42" s="10">
         <f t="shared" si="1"/>
-        <v>5591.0488614137385</v>
+        <v>5237.618838996903</v>
       </c>
       <c r="H42" s="10">
         <f t="shared" si="2"/>
-        <v>6049.8495573593418</v>
+        <v>5667.417116206371</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -1700,15 +1700,15 @@
       </c>
       <c r="F43" s="10">
         <f t="shared" si="0"/>
-        <v>6021.163138752785</v>
+        <v>5640.544067831855</v>
       </c>
       <c r="G43" s="10">
         <f t="shared" si="1"/>
-        <v>5824.3804086632717</v>
+        <v>5456.2006718334405</v>
       </c>
       <c r="H43" s="10">
         <f t="shared" si="2"/>
-        <v>6292.8261199536246</v>
+        <v>5895.034268769894</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -1729,15 +1729,15 @@
       </c>
       <c r="F44" s="10">
         <f t="shared" si="0"/>
-        <v>6264.4541508675939</v>
+        <v>5868.455792446785</v>
       </c>
       <c r="G44" s="10">
         <f t="shared" si="1"/>
-        <v>6059.9889421381113</v>
+        <v>5676.915554522592</v>
       </c>
       <c r="H44" s="10">
         <f t="shared" si="2"/>
-        <v>6527.0279258053815</v>
+        <v>6114.431348076779</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -1758,15 +1758,15 @@
       </c>
       <c r="F45" s="10">
         <f t="shared" si="0"/>
-        <v>6461.3548438498556</v>
+        <v>6052.909694485243</v>
       </c>
       <c r="G45" s="10">
         <f t="shared" si="1"/>
-        <v>6266.7556500924175</v>
+        <v>5870.611805745304</v>
       </c>
       <c r="H45" s="10">
         <f t="shared" si="2"/>
-        <v>6720.1321149851883</v>
+        <v>6295.328736779198</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -1787,15 +1787,15 @@
       </c>
       <c r="F46" s="10">
         <f t="shared" si="0"/>
-        <v>6637.0924388104231</v>
+        <v>6217.538292964837</v>
       </c>
       <c r="G46" s="10">
         <f t="shared" si="1"/>
-        <v>6432.7278584000142</v>
+        <v>6026.092322286877</v>
       </c>
       <c r="H46" s="10">
         <f t="shared" si="2"/>
-        <v>6903.6766908392619</v>
+        <v>6467.27080920922</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -1816,15 +1816,15 @@
       </c>
       <c r="F47" s="10">
         <f t="shared" si="0"/>
-        <v>6818.8983576380524</v>
+        <v>6387.85161504372</v>
       </c>
       <c r="G47" s="10">
         <f t="shared" si="1"/>
-        <v>6603.4043948255021</v>
+        <v>6185.979789686122</v>
       </c>
       <c r="H47" s="10">
         <f t="shared" si="2"/>
-        <v>7093.1434757162051</v>
+        <v>6644.7607268317115</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -1845,15 +1845,15 @@
       </c>
       <c r="F48" s="10">
         <f t="shared" si="0"/>
-        <v>7007.1922223282681</v>
+        <v>6564.242756923248</v>
       </c>
       <c r="G48" s="10">
         <f t="shared" si="1"/>
-        <v>6779.5334291692716</v>
+        <v>6350.975083277601</v>
       </c>
       <c r="H48" s="10">
         <f t="shared" si="2"/>
-        <v>7288.327384485844</v>
+        <v>6827.6063686747375</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -1874,15 +1874,15 @@
       </c>
       <c r="F49" s="10">
         <f t="shared" si="0"/>
-        <v>7202.3047014617887</v>
+        <v>6747.021484450719</v>
       </c>
       <c r="G49" s="10">
         <f t="shared" si="1"/>
-        <v>6966.9806367232941</v>
+        <v>6526.5730882204625</v>
       </c>
       <c r="H49" s="10">
         <f t="shared" si="2"/>
-        <v>7488.9794281631639</v>
+        <v>7015.574485229851</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -1903,15 +1903,15 @@
       </c>
       <c r="F50" s="10">
         <f t="shared" si="0"/>
-        <v>7404.6575001413321</v>
+        <v>6936.58284525409</v>
       </c>
       <c r="G50" s="10">
         <f t="shared" si="1"/>
-        <v>7165.0315273566503</v>
+        <v>6712.104479838293</v>
       </c>
       <c r="H50" s="10">
         <f t="shared" si="2"/>
-        <v>7695.0557028933163</v>
+        <v>7208.623947960539</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
@@ -1932,15 +1932,15 @@
       </c>
       <c r="F51" s="10">
         <f t="shared" si="0"/>
-        <v>7614.1653526288419</v>
+        <v>7132.846963544929</v>
       </c>
       <c r="G51" s="10">
         <f t="shared" si="1"/>
-        <v>7370.6916175997676</v>
+        <v>6904.764066579015</v>
       </c>
       <c r="H51" s="10">
         <f t="shared" si="2"/>
-        <v>7906.2488816923787</v>
+        <v>7406.466857111205</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
@@ -1961,15 +1961,15 @@
       </c>
       <c r="F52" s="10">
         <f t="shared" si="0"/>
-        <v>7830.4749042750991</v>
+        <v>7335.482821474265</v>
       </c>
       <c r="G52" s="10">
         <f t="shared" si="1"/>
-        <v>7579.6048030601796</v>
+        <v>7100.471108854019</v>
       </c>
       <c r="H52" s="10">
         <f t="shared" si="2"/>
-        <v>8121.9394992111547</v>
+        <v>7608.52290593378</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
@@ -1990,15 +1990,15 @@
       </c>
       <c r="F53" s="10">
         <f t="shared" si="0"/>
-        <v>8053.292517641391</v>
+        <v>7544.215343467021</v>
       </c>
       <c r="G53" s="10">
         <f t="shared" si="1"/>
-        <v>7794.2218811145685</v>
+        <v>7301.521480448143</v>
       </c>
       <c r="H53" s="10">
         <f t="shared" si="2"/>
-        <v>8344.3834918815282</v>
+        <v>7816.905425119535</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
@@ -2019,15 +2019,15 @@
       </c>
       <c r="F54" s="10">
         <f t="shared" si="0"/>
-        <v>8282.7509986444893</v>
+        <v>7759.168940307087</v>
       </c>
       <c r="G54" s="10">
         <f t="shared" si="1"/>
-        <v>8016.0512198170982</v>
+        <v>7509.328200122705</v>
       </c>
       <c r="H54" s="10">
         <f t="shared" si="2"/>
-        <v>8584.0919236917889</v>
+        <v>8041.461037033532</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -2048,15 +2048,15 @@
       </c>
       <c r="F55" s="10">
         <f t="shared" si="0"/>
-        <v>8519.3058696354456</v>
+        <v>7980.770339162584</v>
       </c>
       <c r="G55" s="10">
         <f t="shared" si="1"/>
-        <v>8246.1561344467773</v>
+        <v>7724.887367227792</v>
       </c>
       <c r="H55" s="10">
         <f t="shared" si="2"/>
-        <v>8839.5654479278073</v>
+        <v>8280.7851739836</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
@@ -2077,15 +2077,15 @@
       </c>
       <c r="F56" s="10">
         <f t="shared" si="0"/>
-        <v>8763.615220564594</v>
+        <v>8209.63602978473</v>
       </c>
       <c r="G56" s="10">
         <f t="shared" si="1"/>
-        <v>8480.3362890824465</v>
+        <v>7944.264163968725</v>
       </c>
       <c r="H56" s="10">
         <f t="shared" si="2"/>
-        <v>9103.0132353337485</v>
+        <v>8527.579492654695</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
@@ -2106,15 +2106,15 @@
       </c>
       <c r="F57" s="10">
         <f t="shared" si="0"/>
-        <v>9024.2101313285148</v>
+        <v>8453.75781226164</v>
       </c>
       <c r="G57" s="10">
         <f t="shared" si="1"/>
-        <v>8731.6660111281981</v>
+        <v>8179.706443157434</v>
       </c>
       <c r="H57" s="10">
         <f t="shared" si="2"/>
-        <v>9360.5959488703866</v>
+        <v>8768.87948957125</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -2135,15 +2135,15 @@
       </c>
       <c r="F58" s="10">
         <f t="shared" si="0"/>
-        <v>9296.7774701866419</v>
+        <v>8709.095203202918</v>
       </c>
       <c r="G58" s="10">
         <f t="shared" si="1"/>
-        <v>8995.0807202873366</v>
+        <v>8426.46977457499</v>
       </c>
       <c r="H58" s="10">
         <f t="shared" si="2"/>
-        <v>9642.5278605891963</v>
+        <v>9032.989485519216</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -2164,15 +2164,15 @@
       </c>
       <c r="F59" s="10">
         <f t="shared" si="0"/>
-        <v>9573.1244037464839</v>
+        <v>8967.973267263702</v>
       </c>
       <c r="G59" s="10">
         <f t="shared" si="1"/>
-        <v>9258.8779342640391</v>
+        <v>8673.591431324367</v>
       </c>
       <c r="H59" s="10">
         <f t="shared" si="2"/>
-        <v>9939.5843495911486</v>
+        <v>9311.267980593839</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -2193,15 +2193,15 @@
       </c>
       <c r="F60" s="10">
         <f t="shared" si="0"/>
-        <v>9853.1690382229335</v>
+        <v>9230.315287455416</v>
       </c>
       <c r="G60" s="10">
         <f t="shared" si="1"/>
-        <v>9521.0122145606128</v>
+        <v>8919.155274327708</v>
       </c>
       <c r="H60" s="10">
         <f t="shared" si="2"/>
-        <v>10240.609025363985</v>
+        <v>9593.263819283768</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -2222,15 +2222,15 @@
       </c>
       <c r="F61" s="10">
         <f t="shared" si="0"/>
-        <v>10136.374981027133</v>
+        <v>9495.618778466596</v>
       </c>
       <c r="G61" s="10">
         <f t="shared" si="1"/>
-        <v>9786.8542656123373</v>
+        <v>9168.192506750323</v>
       </c>
       <c r="H61" s="10">
         <f t="shared" si="2"/>
-        <v>10535.361464120522</v>
+        <v>9869.383911298337</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
@@ -2251,15 +2251,15 @@
       </c>
       <c r="F62" s="10">
         <f t="shared" si="0"/>
-        <v>10422.85779585946</v>
+        <v>9763.991998806378</v>
       </c>
       <c r="G62" s="10">
         <f t="shared" si="1"/>
-        <v>10056.372212017748</v>
+        <v>9420.673268147892</v>
       </c>
       <c r="H62" s="10">
         <f t="shared" si="2"/>
-        <v>10829.028936381957</v>
+        <v>10144.48762139687</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
@@ -2280,15 +2280,15 @@
       </c>
       <c r="F63" s="10">
         <f t="shared" si="0"/>
-        <v>10711.716917619473</v>
+        <v>10034.591311287395</v>
       </c>
       <c r="G63" s="10">
         <f t="shared" si="1"/>
-        <v>10328.55626511539</v>
+        <v>9675.6516021806</v>
       </c>
       <c r="H63" s="10">
         <f t="shared" si="2"/>
-        <v>11123.643047924596</v>
+        <v>10420.478130351192</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
@@ -2309,15 +2309,15 @@
       </c>
       <c r="F64" s="10">
         <f t="shared" si="0"/>
-        <v>11002.482912422814</v>
+        <v>10306.976956605575</v>
       </c>
       <c r="G64" s="10">
         <f t="shared" si="1"/>
-        <v>10617.678184843586</v>
+        <v>9946.497100238443</v>
       </c>
       <c r="H64" s="10">
         <f t="shared" si="2"/>
-        <v>11419.524958453749</v>
+        <v>10697.656296222922</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
@@ -2338,15 +2338,15 @@
       </c>
       <c r="F65" s="10">
         <f t="shared" si="0"/>
-        <v>11294.823848377913</v>
+        <v>10580.837985461125</v>
       </c>
       <c r="G65" s="10">
         <f t="shared" si="1"/>
-        <v>10911.120725026767</v>
+        <v>10221.39009701292</v>
       </c>
       <c r="H65" s="10">
         <f t="shared" si="2"/>
-        <v>11715.634206751829</v>
+        <v>10975.047429037148</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
@@ -2367,15 +2367,15 @@
       </c>
       <c r="F66" s="10">
         <f t="shared" si="0"/>
-        <v>11588.214253231128</v>
+        <v>10855.682142564694</v>
       </c>
       <c r="G66" s="10">
         <f t="shared" si="1"/>
-        <v>11210.810843896816</v>
+        <v>10502.135740873753</v>
       </c>
       <c r="H66" s="10">
         <f t="shared" si="2"/>
-        <v>12011.827654223589</v>
+        <v>11252.517438496741</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
@@ -2395,16 +2395,16 @@
         <v>9992.8046875</v>
       </c>
       <c r="F67" s="10">
-        <f t="shared" ref="F67:F102" si="3">C67*(116/103)*(126.919/116.048)</f>
-        <v>11882.095700603879</v>
+        <f t="shared" ref="F67:F102" si="3">C67*(116/103)*(118.896/116.048)</f>
+        <v>11130.986301649074</v>
       </c>
       <c r="G67" s="10">
-        <f t="shared" ref="G67:G102" si="4">D67*(116/103)*(126.919/116.048)</f>
-        <v>11506.051637860683</v>
+        <f t="shared" ref="G67:G102" si="4">D67*(116/103)*(118.896/116.048)</f>
+        <v>10778.713317431462</v>
       </c>
       <c r="H67" s="10">
-        <f t="shared" ref="H67:H102" si="5">E67*(116/103)*(126.919/116.048)</f>
-        <v>12308.273699216379</v>
+        <f t="shared" ref="H67:H102" si="5">E67*(116/103)*(118.896/116.048)</f>
+        <v>11530.22407789244</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
@@ -2425,15 +2425,15 @@
       </c>
       <c r="F68" s="10">
         <f t="shared" si="3"/>
-        <v>12177.964880959462</v>
+        <v>11408.152542066644</v>
       </c>
       <c r="G68" s="10">
         <f t="shared" si="4"/>
-        <v>11792.118330429723</v>
+        <v>11046.69672007164</v>
       </c>
       <c r="H68" s="10">
         <f t="shared" si="5"/>
-        <v>12624.725467874925</v>
+        <v>11826.671808227746</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
@@ -2454,15 +2454,15 @@
       </c>
       <c r="F69" s="10">
         <f t="shared" si="3"/>
-        <v>12473.408061510234</v>
+        <v>11684.919711637507</v>
       </c>
       <c r="G69" s="10">
         <f t="shared" si="4"/>
-        <v>12078.62045301121</v>
+        <v>11315.088027649295</v>
       </c>
       <c r="H69" s="10">
         <f t="shared" si="5"/>
-        <v>12946.521478371313</v>
+        <v>12128.125951925525</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
@@ -2483,15 +2483,15 @@
       </c>
       <c r="F70" s="10">
         <f t="shared" si="3"/>
-        <v>12768.283580779194</v>
+        <v>11961.155103808913</v>
       </c>
       <c r="G70" s="10">
         <f t="shared" si="4"/>
-        <v>12364.758113455209</v>
+        <v>11583.137912033428</v>
       </c>
       <c r="H70" s="10">
         <f t="shared" si="5"/>
-        <v>13266.415790387928</v>
+        <v>12427.79861024719</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
@@ -2512,15 +2512,15 @@
       </c>
       <c r="F71" s="10">
         <f t="shared" si="3"/>
-        <v>13063.852184914274</v>
+        <v>12238.039768494613</v>
       </c>
       <c r="G71" s="10">
         <f t="shared" si="4"/>
-        <v>12648.699378311565</v>
+        <v>11849.130242782656</v>
       </c>
       <c r="H71" s="10">
         <f t="shared" si="5"/>
-        <v>13585.916771978935</v>
+        <v>12727.10280195406</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
@@ -2541,15 +2541,15 @@
       </c>
       <c r="F72" s="10">
         <f t="shared" si="3"/>
-        <v>13358.438855464135</v>
+        <v>12514.004571098605</v>
       </c>
       <c r="G72" s="10">
         <f t="shared" si="4"/>
-        <v>12920.625421084153</v>
+        <v>12103.86687623777</v>
       </c>
       <c r="H72" s="10">
         <f t="shared" si="5"/>
-        <v>13905.156736131543</v>
+        <v>13026.16247606029</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
@@ -2570,15 +2570,15 @@
       </c>
       <c r="F73" s="10">
         <f t="shared" si="3"/>
-        <v>13651.74446782946</v>
+        <v>12788.769295748087</v>
       </c>
       <c r="G73" s="10">
         <f t="shared" si="4"/>
-        <v>13192.885854860773</v>
+        <v>12358.91676265592</v>
       </c>
       <c r="H73" s="10">
         <f t="shared" si="5"/>
-        <v>14220.695545178358</v>
+        <v>13321.754958197955</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
@@ -2599,15 +2599,15 @@
       </c>
       <c r="F74" s="10">
         <f t="shared" si="3"/>
-        <v>13945.042701682542</v>
+        <v>13063.527108307248</v>
       </c>
       <c r="G74" s="10">
         <f t="shared" si="4"/>
-        <v>13465.158317090776</v>
+        <v>12613.977917166263</v>
       </c>
       <c r="H74" s="10">
         <f t="shared" si="5"/>
-        <v>14535.189081626235</v>
+        <v>13616.368243123827</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
@@ -2628,15 +2628,15 @@
       </c>
       <c r="F75" s="10">
         <f t="shared" si="3"/>
-        <v>14236.476104743715</v>
+        <v>13336.537972640888</v>
       </c>
       <c r="G75" s="10">
         <f t="shared" si="4"/>
-        <v>13737.707433748577</v>
+        <v>12869.298237797106</v>
       </c>
       <c r="H75" s="10">
         <f t="shared" si="5"/>
-        <v>14847.174685543863</v>
+        <v>13908.63213082693</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
@@ -2657,15 +2657,15 @@
       </c>
       <c r="F76" s="10">
         <f t="shared" si="3"/>
-        <v>14526.563058277108</v>
+        <v>13608.287501295434</v>
       </c>
       <c r="G76" s="10">
         <f t="shared" si="4"/>
-        <v>14009.766992353711</v>
+        <v>13124.15994707559</v>
       </c>
       <c r="H76" s="10">
         <f t="shared" si="5"/>
-        <v>15155.741803010189</v>
+        <v>14197.693626728067</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
@@ -2686,15 +2686,15 @@
       </c>
       <c r="F77" s="10">
         <f t="shared" si="3"/>
-        <v>14816.229875449621</v>
+        <v>13879.643451898126</v>
       </c>
       <c r="G77" s="10">
         <f t="shared" si="4"/>
-        <v>14282.308891939481</v>
+        <v>13379.473506851115</v>
       </c>
       <c r="H77" s="10">
         <f t="shared" si="5"/>
-        <v>15465.253154067039</v>
+        <v>14487.639667866551</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
@@ -2715,15 +2715,15 @@
       </c>
       <c r="F78" s="10">
         <f t="shared" si="3"/>
-        <v>15103.636788237916</v>
+        <v>14148.882354685551</v>
       </c>
       <c r="G78" s="10">
         <f t="shared" si="4"/>
-        <v>14554.048493684641</v>
+        <v>13634.035484877197</v>
       </c>
       <c r="H78" s="10">
         <f t="shared" si="5"/>
-        <v>15768.028571229695</v>
+        <v>14771.27557737554</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
@@ -2744,15 +2744,15 @@
       </c>
       <c r="F79" s="10">
         <f t="shared" si="3"/>
-        <v>15389.418085041934</v>
+        <v>14416.598402438924</v>
       </c>
       <c r="G79" s="10">
         <f t="shared" si="4"/>
-        <v>14825.931234025051</v>
+        <v>13888.731553200407</v>
       </c>
       <c r="H79" s="10">
         <f t="shared" si="5"/>
-        <v>16071.757844745585</v>
+        <v>15055.805046595633</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
@@ -2773,15 +2773,15 @@
       </c>
       <c r="F80" s="10">
         <f t="shared" si="3"/>
-        <v>15676.778912329535</v>
+        <v>14685.794132953557</v>
       </c>
       <c r="G80" s="10">
         <f t="shared" si="4"/>
-        <v>15097.661213007503</v>
+        <v>14143.284516752734</v>
       </c>
       <c r="H80" s="10">
         <f t="shared" si="5"/>
-        <v>16377.564432160627</v>
+        <v>15342.280515337894</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
@@ -2802,15 +2802,15 @@
       </c>
       <c r="F81" s="10">
         <f t="shared" si="3"/>
-        <v>15956.8000327267</v>
+        <v>14948.114125474309</v>
       </c>
       <c r="G81" s="10">
         <f t="shared" si="4"/>
-        <v>15368.551605943858</v>
+        <v>14397.050967469811</v>
       </c>
       <c r="H81" s="10">
         <f t="shared" si="5"/>
-        <v>16670.026653393139</v>
+        <v>15616.255162598434</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
@@ -2831,15 +2831,15 @@
       </c>
       <c r="F82" s="10">
         <f t="shared" si="3"/>
-        <v>16239.711180753595</v>
+        <v>15213.141456731297</v>
       </c>
       <c r="G82" s="10">
         <f t="shared" si="4"/>
-        <v>15639.896674418073</v>
+        <v>14651.243352071882</v>
       </c>
       <c r="H82" s="10">
         <f t="shared" si="5"/>
-        <v>16968.940937020016</v>
+        <v>15896.274014512657</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
@@ -2860,15 +2860,15 @@
       </c>
       <c r="F83" s="10">
         <f t="shared" si="3"/>
-        <v>16524.012358732667</v>
+        <v>15479.47094921863</v>
       </c>
       <c r="G83" s="10">
         <f t="shared" si="4"/>
-        <v>15911.026433576739</v>
+        <v>14905.234037823651</v>
       </c>
       <c r="H83" s="10">
         <f t="shared" si="5"/>
-        <v>17271.112525822871</v>
+        <v>16179.34426579343</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
@@ -2889,15 +2889,15 @@
       </c>
       <c r="F84" s="10">
         <f t="shared" si="3"/>
-        <v>16801.336682427973</v>
+        <v>15739.264619118936</v>
       </c>
       <c r="G84" s="10">
         <f t="shared" si="4"/>
-        <v>16181.553567220943</v>
+        <v>15158.660192156425</v>
       </c>
       <c r="H84" s="10">
         <f t="shared" si="5"/>
-        <v>17563.710668578606</v>
+        <v>16453.446242495782</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
@@ -2918,15 +2918,15 @@
       </c>
       <c r="F85" s="10">
         <f t="shared" si="3"/>
-        <v>17075.339490173727</v>
+        <v>15995.946737869788</v>
       </c>
       <c r="G85" s="10">
         <f t="shared" si="4"/>
-        <v>16452.3308926955</v>
+        <v>15412.320722806866</v>
       </c>
       <c r="H85" s="10">
         <f t="shared" si="5"/>
-        <v>17848.178779693113</v>
+        <v>16719.932115683172</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
@@ -2947,15 +2947,15 @@
       </c>
       <c r="F86" s="10">
         <f t="shared" si="3"/>
-        <v>17356.275730069203</v>
+        <v>16259.12400194067</v>
       </c>
       <c r="G86" s="10">
         <f t="shared" si="4"/>
-        <v>16678.946954421594</v>
+        <v>15624.611579770639</v>
       </c>
       <c r="H86" s="10">
         <f t="shared" si="5"/>
-        <v>18147.124337298785</v>
+        <v>16999.980264637103</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
@@ -2976,15 +2976,15 @@
       </c>
       <c r="F87" s="10">
         <f t="shared" si="3"/>
-        <v>17622.317218662014</v>
+        <v>16508.348064750266</v>
       </c>
       <c r="G87" s="10">
         <f t="shared" si="4"/>
-        <v>16881.436344353086</v>
+        <v>15814.30089740862</v>
       </c>
       <c r="H87" s="10">
         <f t="shared" si="5"/>
-        <v>18421.816924349347</v>
+        <v>17257.308559297187</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
@@ -3005,15 +3005,15 @@
       </c>
       <c r="F88" s="10">
         <f t="shared" si="3"/>
-        <v>17622.317218662014</v>
+        <v>16508.348064750266</v>
       </c>
       <c r="G88" s="10">
         <f t="shared" si="4"/>
-        <v>16881.436344353086</v>
+        <v>15814.30089740862</v>
       </c>
       <c r="H88" s="10">
         <f t="shared" si="5"/>
-        <v>18421.816924349347</v>
+        <v>17257.308559297187</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
@@ -3034,15 +3034,15 @@
       </c>
       <c r="F89" s="10">
         <f t="shared" si="3"/>
-        <v>17622.317218662014</v>
+        <v>16508.348064750266</v>
       </c>
       <c r="G89" s="10">
         <f t="shared" si="4"/>
-        <v>16881.436344353086</v>
+        <v>15814.30089740862</v>
       </c>
       <c r="H89" s="10">
         <f t="shared" si="5"/>
-        <v>18421.816924349347</v>
+        <v>17257.308559297187</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
@@ -3063,15 +3063,15 @@
       </c>
       <c r="F90" s="10">
         <f t="shared" si="3"/>
-        <v>17622.317218662014</v>
+        <v>16508.348064750266</v>
       </c>
       <c r="G90" s="10">
         <f t="shared" si="4"/>
-        <v>16881.436344353086</v>
+        <v>15814.30089740862</v>
       </c>
       <c r="H90" s="10">
         <f t="shared" si="5"/>
-        <v>18421.816924349347</v>
+        <v>17257.308559297187</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
@@ -3092,15 +3092,15 @@
       </c>
       <c r="F91" s="10">
         <f t="shared" si="3"/>
-        <v>17622.317218662014</v>
+        <v>16508.348064750266</v>
       </c>
       <c r="G91" s="10">
         <f t="shared" si="4"/>
-        <v>16881.436344353086</v>
+        <v>15814.30089740862</v>
       </c>
       <c r="H91" s="10">
         <f t="shared" si="5"/>
-        <v>18421.816924349347</v>
+        <v>17257.308559297187</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
@@ -3121,15 +3121,15 @@
       </c>
       <c r="F92" s="10">
         <f t="shared" si="3"/>
-        <v>17622.317218662014</v>
+        <v>16508.348064750266</v>
       </c>
       <c r="G92" s="10">
         <f t="shared" si="4"/>
-        <v>16881.436344353086</v>
+        <v>15814.30089740862</v>
       </c>
       <c r="H92" s="10">
         <f t="shared" si="5"/>
-        <v>18421.816924349347</v>
+        <v>17257.308559297187</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
@@ -3150,15 +3150,15 @@
       </c>
       <c r="F93" s="10">
         <f t="shared" si="3"/>
-        <v>17622.317218662014</v>
+        <v>16508.348064750266</v>
       </c>
       <c r="G93" s="10">
         <f t="shared" si="4"/>
-        <v>16881.436344353086</v>
+        <v>15814.30089740862</v>
       </c>
       <c r="H93" s="10">
         <f t="shared" si="5"/>
-        <v>18421.816924349347</v>
+        <v>17257.308559297187</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
@@ -3179,15 +3179,15 @@
       </c>
       <c r="F94" s="10">
         <f t="shared" si="3"/>
-        <v>17622.317218662014</v>
+        <v>16508.348064750266</v>
       </c>
       <c r="G94" s="10">
         <f t="shared" si="4"/>
-        <v>16881.436344353086</v>
+        <v>15814.30089740862</v>
       </c>
       <c r="H94" s="10">
         <f t="shared" si="5"/>
-        <v>18421.816924349347</v>
+        <v>17257.308559297187</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
@@ -3208,15 +3208,15 @@
       </c>
       <c r="F95" s="10">
         <f t="shared" si="3"/>
-        <v>17622.317218662014</v>
+        <v>16508.348064750266</v>
       </c>
       <c r="G95" s="10">
         <f t="shared" si="4"/>
-        <v>16881.436344353086</v>
+        <v>15814.30089740862</v>
       </c>
       <c r="H95" s="10">
         <f t="shared" si="5"/>
-        <v>18421.816924349347</v>
+        <v>17257.308559297187</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
@@ -3237,15 +3237,15 @@
       </c>
       <c r="F96" s="10">
         <f t="shared" si="3"/>
-        <v>17622.317218662014</v>
+        <v>16508.348064750266</v>
       </c>
       <c r="G96" s="10">
         <f t="shared" si="4"/>
-        <v>16881.436344353086</v>
+        <v>15814.30089740862</v>
       </c>
       <c r="H96" s="10">
         <f t="shared" si="5"/>
-        <v>18421.816924349347</v>
+        <v>17257.308559297187</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
@@ -3266,15 +3266,15 @@
       </c>
       <c r="F97" s="10">
         <f t="shared" si="3"/>
-        <v>17622.317218662014</v>
+        <v>16508.348064750266</v>
       </c>
       <c r="G97" s="10">
         <f t="shared" si="4"/>
-        <v>16881.436344353086</v>
+        <v>15814.30089740862</v>
       </c>
       <c r="H97" s="10">
         <f t="shared" si="5"/>
-        <v>18421.816924349347</v>
+        <v>17257.308559297187</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
@@ -3295,15 +3295,15 @@
       </c>
       <c r="F98" s="10">
         <f t="shared" si="3"/>
-        <v>17622.317218662014</v>
+        <v>16508.348064750266</v>
       </c>
       <c r="G98" s="10">
         <f t="shared" si="4"/>
-        <v>16881.436344353086</v>
+        <v>15814.30089740862</v>
       </c>
       <c r="H98" s="10">
         <f t="shared" si="5"/>
-        <v>18421.816924349347</v>
+        <v>17257.308559297187</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
@@ -3324,15 +3324,15 @@
       </c>
       <c r="F99" s="10">
         <f t="shared" si="3"/>
-        <v>17622.317218662014</v>
+        <v>16508.348064750266</v>
       </c>
       <c r="G99" s="10">
         <f t="shared" si="4"/>
-        <v>16881.436344353086</v>
+        <v>15814.30089740862</v>
       </c>
       <c r="H99" s="10">
         <f t="shared" si="5"/>
-        <v>18421.816924349347</v>
+        <v>17257.308559297187</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
@@ -3353,15 +3353,15 @@
       </c>
       <c r="F100" s="10">
         <f t="shared" si="3"/>
-        <v>17622.317218662014</v>
+        <v>16508.348064750266</v>
       </c>
       <c r="G100" s="10">
         <f t="shared" si="4"/>
-        <v>16881.436344353086</v>
+        <v>15814.30089740862</v>
       </c>
       <c r="H100" s="10">
         <f t="shared" si="5"/>
-        <v>18421.816924349347</v>
+        <v>17257.308559297187</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
@@ -3382,15 +3382,15 @@
       </c>
       <c r="F101" s="10">
         <f t="shared" si="3"/>
-        <v>17622.317218662014</v>
+        <v>16508.348064750266</v>
       </c>
       <c r="G101" s="10">
         <f t="shared" si="4"/>
-        <v>16881.436344353086</v>
+        <v>15814.30089740862</v>
       </c>
       <c r="H101" s="10">
         <f t="shared" si="5"/>
-        <v>18421.816924349347</v>
+        <v>17257.308559297187</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.2">
@@ -3411,15 +3411,15 @@
       </c>
       <c r="F102" s="10">
         <f t="shared" si="3"/>
-        <v>17622.317218662014</v>
+        <v>16508.348064750266</v>
       </c>
       <c r="G102" s="10">
         <f t="shared" si="4"/>
-        <v>16881.436344353086</v>
+        <v>15814.30089740862</v>
       </c>
       <c r="H102" s="10">
         <f t="shared" si="5"/>
-        <v>18421.816924349347</v>
+        <v>17257.308559297187</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3435,7 +3435,11 @@
       <c r="H103" s="9"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A104" s="1"/>
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>2025 USD = 2019 USD x (PHC 2024 / PHC 2019) x (PCE-Health 2025 / PCE-Health 2024) = x (116.0 / 103.0) x (118.896 / 116.048). PHC: MEPS price index table (2017=100); PCE-Health: BEA via FRED DHLTRG3A086NBEA (2017=100).</t>
+        </is>
+      </c>
       <c r="B104" s="1"/>
     </row>
   </sheetData>
